--- a/experimental/attention/quant_lightning_indexer/tests/pytest/excel/example.xlsx
+++ b/experimental/attention/quant_lightning_indexer/tests/pytest/excel/example.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\pytest\qli_up\ops-transformer\experimental\attention\quant_lightning_indexer\tests\pytest\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Users\z00947698\code_1\geneva-2\ops-transformer_genev_S\experimental\attention\quant_lightning_indexer\tests\pytest\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D648CCF-68B4-4B83-A066-283E1E098596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A0139D-3399-42DF-81A2-4E095900E1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Testcase_Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,18 +76,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FLOAT8_E4M3FN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dequant_dtype</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FP32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>actual_seq_dtype</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -100,18 +92,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0,0,0,0,0,0,0,0,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>act_seq_k</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1234,781,79,552,90,1022,111,1344</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>query_quant_mode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -160,10 +144,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0,255</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>k_scale_datarange</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,6 +157,30 @@
   </si>
   <si>
     <t>layout_query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FP16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,352,14,461</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-255,255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -220,11 +224,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -568,7 +575,8 @@
   <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="24" max="25" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.25" customWidth="1"/>
+    <col min="25" max="25" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.15">
@@ -609,52 +617,52 @@
         <v>12</v>
       </c>
       <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
-        <v>38</v>
-      </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>24</v>
       </c>
-      <c r="U1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" t="s">
         <v>28</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
         <v>32</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.15">
@@ -662,19 +670,19 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>64</v>
@@ -686,25 +694,25 @@
         <v>128</v>
       </c>
       <c r="J2">
-        <v>784</v>
+        <v>128</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
         <v>15</v>
       </c>
-      <c r="N2" t="s">
-        <v>17</v>
-      </c>
       <c r="O2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -713,10 +721,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="U2">
         <v>512</v>
@@ -725,22 +733,22 @@
         <v>3</v>
       </c>
       <c r="W2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>-171171</v>
+      </c>
+      <c r="AA2" t="s">
         <v>31</v>
       </c>
-      <c r="X2" s="1">
-        <v>-448448</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>-171171</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>36</v>
-      </c>
       <c r="AB2">
-        <v>128</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/experimental/attention/quant_lightning_indexer/tests/pytest/excel/example.xlsx
+++ b/experimental/attention/quant_lightning_indexer/tests/pytest/excel/example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Users\z00947698\code_1\geneva-2\ops-transformer_genev_S\experimental\attention\quant_lightning_indexer\tests\pytest\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A0139D-3399-42DF-81A2-4E095900E1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5203EEB9-A22C-4F7F-A1FB-CE7EA767A56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/experimental/attention/quant_lightning_indexer/tests/pytest/excel/example.xlsx
+++ b/experimental/attention/quant_lightning_indexer/tests/pytest/excel/example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Users\z00947698\code_1\geneva-2\ops-transformer_genev_S\experimental\attention\quant_lightning_indexer\tests\pytest\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5203EEB9-A22C-4F7F-A1FB-CE7EA767A56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3596278-B382-47C4-8E29-CAA30B284DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Testcase_Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -181,6 +181,10 @@
   </si>
   <si>
     <t>0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-171,171</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -224,11 +228,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
@@ -738,11 +739,11 @@
       <c r="X2" t="s">
         <v>39</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Z2" s="1">
-        <v>-171171</v>
+      <c r="Z2" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AA2" t="s">
         <v>31</v>
